--- a/tests/output/teklif-QBR2525-TEST-2-ROWS/teklif-QBR2525-TEST-2-ROWS.xlsx
+++ b/tests/output/teklif-QBR2525-TEST-2-ROWS/teklif-QBR2525-TEST-2-ROWS.xlsx
@@ -7,7 +7,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teklif" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="adres" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Teklif'!$26:$26</definedName>
@@ -313,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,29 +472,278 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1016,811 +1264,1796 @@
   </cols>
   <sheetData>
     <row r="1" ht="11.1" customFormat="1" customHeight="1" s="62">
-      <c r="A1" s="68" t="n"/>
-      <c r="B1" s="60" t="n"/>
-      <c r="C1" s="58" t="inlineStr">
+      <c r="A1" s="79" t="n"/>
+      <c r="B1" s="80" t="n"/>
+      <c r="C1" s="81" t="inlineStr">
         <is>
           <t>TEKLİF FORMU</t>
         </is>
       </c>
-      <c r="D1" s="59" t="n"/>
-      <c r="E1" s="59" t="n"/>
-      <c r="F1" s="60" t="n"/>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="D1" s="82" t="n"/>
+      <c r="E1" s="82" t="n"/>
+      <c r="F1" s="80" t="n"/>
+      <c r="G1" s="83" t="inlineStr">
         <is>
           <t>Doküman No.</t>
         </is>
       </c>
-      <c r="H1" s="48" t="inlineStr">
+      <c r="H1" s="84" t="inlineStr">
         <is>
           <t>ANT-FRM-022</t>
         </is>
       </c>
-      <c r="I1" s="7" t="n"/>
+      <c r="I1" s="85" t="n"/>
+      <c r="J1" s="86" t="n"/>
+      <c r="K1" s="86" t="n"/>
+      <c r="L1" s="86" t="n"/>
     </row>
     <row r="2" ht="11.1" customFormat="1" customHeight="1" s="62">
-      <c r="A2" s="61" t="n"/>
-      <c r="B2" s="63" t="n"/>
-      <c r="C2" s="61" t="n"/>
-      <c r="F2" s="63" t="n"/>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="A2" s="87" t="n"/>
+      <c r="B2" s="88" t="n"/>
+      <c r="C2" s="87" t="n"/>
+      <c r="D2" s="86" t="n"/>
+      <c r="E2" s="86" t="n"/>
+      <c r="F2" s="88" t="n"/>
+      <c r="G2" s="89" t="inlineStr">
         <is>
           <t>İlk Yayın Tarihi</t>
         </is>
       </c>
-      <c r="H2" s="49" t="n">
+      <c r="H2" s="90" t="n">
         <v>45420</v>
       </c>
+      <c r="I2" s="86" t="n"/>
+      <c r="J2" s="86" t="n"/>
+      <c r="K2" s="86" t="n"/>
+      <c r="L2" s="86" t="n"/>
     </row>
     <row r="3" ht="11.1" customFormat="1" customHeight="1" s="62">
-      <c r="A3" s="61" t="n"/>
-      <c r="B3" s="63" t="n"/>
-      <c r="C3" s="61" t="n"/>
-      <c r="F3" s="63" t="n"/>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="A3" s="87" t="n"/>
+      <c r="B3" s="88" t="n"/>
+      <c r="C3" s="87" t="n"/>
+      <c r="D3" s="86" t="n"/>
+      <c r="E3" s="86" t="n"/>
+      <c r="F3" s="88" t="n"/>
+      <c r="G3" s="89" t="inlineStr">
         <is>
           <t>Revizyon No.</t>
         </is>
       </c>
-      <c r="H3" s="50" t="inlineStr">
+      <c r="H3" s="91" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
+      <c r="I3" s="86" t="n"/>
+      <c r="J3" s="86" t="n"/>
+      <c r="K3" s="86" t="n"/>
+      <c r="L3" s="86" t="n"/>
     </row>
     <row r="4" ht="11.1" customFormat="1" customHeight="1" s="62">
-      <c r="A4" s="61" t="n"/>
-      <c r="B4" s="63" t="n"/>
-      <c r="C4" s="61" t="n"/>
-      <c r="F4" s="63" t="n"/>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="A4" s="87" t="n"/>
+      <c r="B4" s="88" t="n"/>
+      <c r="C4" s="87" t="n"/>
+      <c r="D4" s="86" t="n"/>
+      <c r="E4" s="86" t="n"/>
+      <c r="F4" s="88" t="n"/>
+      <c r="G4" s="89" t="inlineStr">
         <is>
           <t>Revizyon Tarihi</t>
         </is>
       </c>
-      <c r="H4" s="49" t="n">
+      <c r="H4" s="90" t="n">
         <v>45950</v>
       </c>
-      <c r="L4" s="9" t="n"/>
+      <c r="I4" s="86" t="n"/>
+      <c r="J4" s="86" t="n"/>
+      <c r="K4" s="86" t="n"/>
+      <c r="L4" s="92" t="n"/>
     </row>
     <row r="5" ht="11.1" customFormat="1" customHeight="1" s="62">
-      <c r="A5" s="61" t="n"/>
-      <c r="B5" s="63" t="n"/>
-      <c r="C5" s="64" t="n"/>
-      <c r="D5" s="65" t="n"/>
-      <c r="E5" s="65" t="n"/>
-      <c r="F5" s="66" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="A5" s="87" t="n"/>
+      <c r="B5" s="88" t="n"/>
+      <c r="C5" s="93" t="n"/>
+      <c r="D5" s="94" t="n"/>
+      <c r="E5" s="94" t="n"/>
+      <c r="F5" s="95" t="n"/>
+      <c r="G5" s="96" t="inlineStr">
         <is>
           <t>Sayfa No.</t>
         </is>
       </c>
-      <c r="H5" s="50" t="inlineStr">
+      <c r="H5" s="91" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
+      <c r="I5" s="86" t="n"/>
+      <c r="J5" s="86" t="n"/>
+      <c r="K5" s="86" t="n"/>
+      <c r="L5" s="92" t="n"/>
     </row>
     <row r="6" ht="35.25" customHeight="1" s="78">
-      <c r="A6" s="67" t="n"/>
-      <c r="B6" s="59" t="n"/>
-      <c r="C6" s="59" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="A6" s="97" t="n"/>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="98" t="n"/>
+      <c r="E6" s="99" t="n"/>
+      <c r="F6" s="99" t="n"/>
+      <c r="G6" s="99" t="n"/>
+      <c r="H6" s="100" t="inlineStr">
         <is>
           <t>Teklif</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
+      <c r="I6" s="101" t="n"/>
+      <c r="J6" s="86" t="n"/>
+      <c r="K6" s="86" t="n"/>
+      <c r="L6" s="86" t="n"/>
     </row>
     <row r="7" ht="14.25" customHeight="1" s="78">
-      <c r="A7" s="73" t="inlineStr">
+      <c r="A7" s="102" t="inlineStr">
         <is>
           <t>Antsis Elektronik Sanayi ve Ticaret Ltd. Şti.</t>
         </is>
       </c>
-      <c r="D7" s="62" t="n"/>
-      <c r="E7" s="62" t="n"/>
-      <c r="F7" s="62" t="n"/>
-      <c r="G7" s="62" t="n"/>
-      <c r="H7" s="17" t="n"/>
+      <c r="B7" s="86" t="n"/>
+      <c r="C7" s="86" t="n"/>
+      <c r="D7" s="103" t="n"/>
+      <c r="E7" s="103" t="n"/>
+      <c r="F7" s="103" t="n"/>
+      <c r="G7" s="103" t="n"/>
+      <c r="H7" s="104" t="n"/>
+      <c r="I7" s="86" t="n"/>
+      <c r="J7" s="86" t="n"/>
+      <c r="K7" s="86" t="n"/>
+      <c r="L7" s="86" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="78">
-      <c r="A8" s="71" t="n"/>
-      <c r="B8" s="62" t="n"/>
-      <c r="C8" s="62" t="n"/>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="62" t="n"/>
-      <c r="F8" s="62" t="n"/>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="A8" s="105" t="n"/>
+      <c r="B8" s="103" t="n"/>
+      <c r="C8" s="103" t="n"/>
+      <c r="D8" s="103" t="n"/>
+      <c r="E8" s="103" t="n"/>
+      <c r="F8" s="103" t="n"/>
+      <c r="G8" s="106" t="inlineStr">
         <is>
           <t>Tarih :</t>
         </is>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="107" t="n">
         <v>46212</v>
       </c>
+      <c r="I8" s="86" t="n"/>
+      <c r="J8" s="86" t="n"/>
+      <c r="K8" s="86" t="n"/>
+      <c r="L8" s="86" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="78">
-      <c r="A9" s="71" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">Kemal Nehrozoğlu Cad. Gosb Teknopark </t>
         </is>
       </c>
-      <c r="B9" s="62" t="n"/>
-      <c r="C9" s="62" t="n"/>
-      <c r="D9" s="62" t="n"/>
-      <c r="E9" s="62" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="B9" s="103" t="n"/>
+      <c r="C9" s="103" t="n"/>
+      <c r="D9" s="103" t="n"/>
+      <c r="E9" s="103" t="n"/>
+      <c r="F9" s="108" t="n"/>
+      <c r="G9" s="106" t="inlineStr">
         <is>
           <t>Teklif No :</t>
         </is>
       </c>
-      <c r="H9" s="79" t="inlineStr">
+      <c r="H9" s="109" t="inlineStr">
         <is>
           <t>TEST-2-ROWS</t>
         </is>
       </c>
+      <c r="I9" s="86" t="n"/>
+      <c r="J9" s="86" t="n"/>
+      <c r="K9" s="86" t="n"/>
+      <c r="L9" s="86" t="n"/>
     </row>
     <row r="10" ht="14.25" customHeight="1" s="78">
-      <c r="A10" s="71" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">No: 507 /9 / Hibrid 1. Bina, 1. Kat, A-5 </t>
         </is>
       </c>
-      <c r="B10" s="62" t="n"/>
-      <c r="C10" s="62" t="n"/>
-      <c r="D10" s="62" t="n"/>
-      <c r="E10" s="62" t="n"/>
-      <c r="F10" s="74" t="inlineStr">
+      <c r="B10" s="103" t="n"/>
+      <c r="C10" s="103" t="n"/>
+      <c r="D10" s="103" t="n"/>
+      <c r="E10" s="103" t="n"/>
+      <c r="F10" s="110" t="inlineStr">
         <is>
           <t xml:space="preserve">                           Teklif Geçerlilik Süresi :</t>
         </is>
       </c>
-      <c r="H10" s="80" t="n">
+      <c r="G10" s="86" t="n"/>
+      <c r="H10" s="111" t="n">
         <v>46242</v>
       </c>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="112" t="n"/>
+      <c r="J10" s="86" t="n"/>
+      <c r="K10" s="86" t="n"/>
+      <c r="L10" s="86" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1" s="78">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gebze Kocaeli </t>
         </is>
       </c>
-      <c r="B11" s="62" t="n"/>
-      <c r="C11" s="62" t="n"/>
-      <c r="D11" s="62" t="n"/>
-      <c r="E11" s="62" t="n"/>
-      <c r="G11" s="74" t="inlineStr">
+      <c r="B11" s="103" t="n"/>
+      <c r="C11" s="103" t="n"/>
+      <c r="D11" s="103" t="n"/>
+      <c r="E11" s="103" t="n"/>
+      <c r="F11" s="86" t="n"/>
+      <c r="G11" s="110" t="inlineStr">
         <is>
           <t>Hazırlayan :</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="113" t="inlineStr">
         <is>
           <t>Alican Uzun</t>
         </is>
       </c>
+      <c r="I11" s="86" t="n"/>
+      <c r="J11" s="86" t="n"/>
+      <c r="K11" s="86" t="n"/>
+      <c r="L11" s="86" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1" s="78">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>Tel/Faks +90 262 678 88 33</t>
         </is>
       </c>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="62" t="n"/>
-      <c r="F12" s="62" t="n"/>
-      <c r="H12" s="17" t="n"/>
+      <c r="B12" s="86" t="n"/>
+      <c r="C12" s="86" t="n"/>
+      <c r="D12" s="114" t="n"/>
+      <c r="E12" s="103" t="n"/>
+      <c r="F12" s="103" t="n"/>
+      <c r="G12" s="86" t="n"/>
+      <c r="H12" s="104" t="n"/>
+      <c r="I12" s="86" t="n"/>
+      <c r="J12" s="86" t="n"/>
+      <c r="K12" s="86" t="n"/>
+      <c r="L12" s="86" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="78">
-      <c r="A13" s="71" t="n"/>
-      <c r="B13" s="62" t="n"/>
-      <c r="C13" s="62" t="n"/>
-      <c r="D13" s="62" t="n"/>
-      <c r="E13" s="62" t="n"/>
-      <c r="F13" s="62" t="n"/>
-      <c r="G13" s="62" t="n"/>
-      <c r="H13" s="17" t="n"/>
+      <c r="A13" s="105" t="n"/>
+      <c r="B13" s="103" t="n"/>
+      <c r="C13" s="103" t="n"/>
+      <c r="D13" s="103" t="n"/>
+      <c r="E13" s="103" t="n"/>
+      <c r="F13" s="103" t="n"/>
+      <c r="G13" s="103" t="n"/>
+      <c r="H13" s="104" t="n"/>
+      <c r="I13" s="86" t="n"/>
+      <c r="J13" s="86" t="n"/>
+      <c r="K13" s="86" t="n"/>
+      <c r="L13" s="86" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="78">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Sayın Test Kisi</t>
         </is>
       </c>
-      <c r="B14" s="62" t="n"/>
-      <c r="C14" s="62" t="n"/>
-      <c r="D14" s="62" t="n"/>
-      <c r="E14" s="62" t="n"/>
-      <c r="F14" s="62" t="n"/>
-      <c r="G14" s="62" t="n"/>
-      <c r="H14" s="17" t="n"/>
+      <c r="B14" s="103" t="n"/>
+      <c r="C14" s="103" t="n"/>
+      <c r="D14" s="103" t="n"/>
+      <c r="E14" s="103" t="n"/>
+      <c r="F14" s="103" t="n"/>
+      <c r="G14" s="103" t="n"/>
+      <c r="H14" s="104" t="n"/>
+      <c r="I14" s="86" t="n"/>
+      <c r="J14" s="86" t="n"/>
+      <c r="K14" s="86" t="n"/>
+      <c r="L14" s="86" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1" s="78">
-      <c r="A15" s="71" t="n"/>
-      <c r="C15" s="62" t="n"/>
-      <c r="D15" s="62" t="n"/>
-      <c r="E15" s="62" t="n"/>
-      <c r="F15" s="62" t="n"/>
-      <c r="G15" s="62" t="n"/>
-      <c r="H15" s="17" t="n"/>
+      <c r="A15" s="105" t="n"/>
+      <c r="B15" s="86" t="n"/>
+      <c r="C15" s="103" t="n"/>
+      <c r="D15" s="103" t="n"/>
+      <c r="E15" s="103" t="n"/>
+      <c r="F15" s="103" t="n"/>
+      <c r="G15" s="103" t="n"/>
+      <c r="H15" s="104" t="n"/>
+      <c r="I15" s="86" t="n"/>
+      <c r="J15" s="86" t="n"/>
+      <c r="K15" s="86" t="n"/>
+      <c r="L15" s="86" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="78">
-      <c r="A16" s="71" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>Roketsan Roket Sanayii ve Ticaret A.Ş.</t>
         </is>
       </c>
-      <c r="B16" s="62" t="n"/>
-      <c r="C16" s="62" t="n"/>
-      <c r="D16" s="62" t="n"/>
-      <c r="E16" s="62" t="n"/>
-      <c r="F16" s="62" t="n"/>
-      <c r="G16" s="62" t="n"/>
-      <c r="H16" s="17" t="n"/>
+      <c r="B16" s="103" t="n"/>
+      <c r="C16" s="103" t="n"/>
+      <c r="D16" s="103" t="n"/>
+      <c r="E16" s="103" t="n"/>
+      <c r="F16" s="103" t="n"/>
+      <c r="G16" s="103" t="n"/>
+      <c r="H16" s="104" t="n"/>
+      <c r="I16" s="86" t="n"/>
+      <c r="J16" s="86" t="n"/>
+      <c r="K16" s="86" t="n"/>
+      <c r="L16" s="86" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" s="78">
-      <c r="A17" s="71" t="inlineStr">
+      <c r="A17" s="105" t="inlineStr">
         <is>
           <t>Kemalpaşa Mahallesi Şehit Yüzbaşı Adem Kutlu Sok.</t>
         </is>
       </c>
-      <c r="B17" s="62" t="n"/>
-      <c r="C17" s="62" t="n"/>
-      <c r="D17" s="62" t="n"/>
-      <c r="E17" s="62" t="n"/>
-      <c r="F17" s="62" t="n"/>
-      <c r="G17" s="62" t="n"/>
-      <c r="H17" s="17" t="n"/>
+      <c r="B17" s="103" t="n"/>
+      <c r="C17" s="103" t="n"/>
+      <c r="D17" s="103" t="n"/>
+      <c r="E17" s="103" t="n"/>
+      <c r="F17" s="103" t="n"/>
+      <c r="G17" s="103" t="n"/>
+      <c r="H17" s="104" t="n"/>
+      <c r="I17" s="86" t="n"/>
+      <c r="J17" s="86" t="n"/>
+      <c r="K17" s="86" t="n"/>
+      <c r="L17" s="86" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1" s="78">
-      <c r="A18" s="71" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>No:21 06780 Elmadağ, ANKARA</t>
         </is>
       </c>
-      <c r="B18" s="62" t="n"/>
-      <c r="C18" s="62" t="n"/>
-      <c r="D18" s="62" t="n"/>
-      <c r="E18" s="62" t="n"/>
-      <c r="F18" s="62" t="n"/>
-      <c r="G18" s="62" t="n"/>
-      <c r="H18" s="17" t="n"/>
+      <c r="B18" s="103" t="n"/>
+      <c r="C18" s="103" t="n"/>
+      <c r="D18" s="103" t="n"/>
+      <c r="E18" s="103" t="n"/>
+      <c r="F18" s="103" t="n"/>
+      <c r="G18" s="103" t="n"/>
+      <c r="H18" s="104" t="n"/>
+      <c r="I18" s="86" t="n"/>
+      <c r="J18" s="86" t="n"/>
+      <c r="K18" s="86" t="n"/>
+      <c r="L18" s="86" t="n"/>
     </row>
     <row r="19" ht="13.95" customHeight="1" s="78">
-      <c r="A19" s="76" t="inlineStr">
+      <c r="A19" s="116" t="inlineStr">
         <is>
           <t>Tel : +90 312 860 55 00</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="62" t="n"/>
-      <c r="E19" s="62" t="n"/>
-      <c r="F19" s="62" t="n"/>
-      <c r="G19" s="62" t="n"/>
-      <c r="H19" s="17" t="n"/>
+      <c r="B19" s="86" t="n"/>
+      <c r="C19" s="103" t="n"/>
+      <c r="D19" s="103" t="n"/>
+      <c r="E19" s="103" t="n"/>
+      <c r="F19" s="103" t="n"/>
+      <c r="G19" s="103" t="n"/>
+      <c r="H19" s="104" t="n"/>
+      <c r="I19" s="86" t="n"/>
+      <c r="J19" s="86" t="n"/>
+      <c r="K19" s="86" t="n"/>
+      <c r="L19" s="86" t="n"/>
     </row>
     <row r="20" ht="14.25" customHeight="1" s="78">
-      <c r="A20" s="71" t="n"/>
-      <c r="B20" s="62" t="n"/>
-      <c r="C20" s="62" t="n"/>
-      <c r="D20" s="62" t="n"/>
-      <c r="E20" s="62" t="n"/>
-      <c r="F20" s="62" t="n"/>
-      <c r="G20" s="62" t="n"/>
-      <c r="H20" s="17" t="n"/>
+      <c r="A20" s="105" t="n"/>
+      <c r="B20" s="103" t="n"/>
+      <c r="C20" s="103" t="n"/>
+      <c r="D20" s="103" t="n"/>
+      <c r="E20" s="103" t="n"/>
+      <c r="F20" s="103" t="n"/>
+      <c r="G20" s="103" t="n"/>
+      <c r="H20" s="104" t="n"/>
+      <c r="I20" s="86" t="n"/>
+      <c r="J20" s="86" t="n"/>
+      <c r="K20" s="86" t="n"/>
+      <c r="L20" s="86" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="78">
-      <c r="A21" s="26" t="n"/>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="28" t="n"/>
+      <c r="A21" s="117" t="n"/>
+      <c r="B21" s="118" t="n"/>
+      <c r="C21" s="118" t="n"/>
+      <c r="D21" s="118" t="n"/>
+      <c r="E21" s="118" t="n"/>
+      <c r="F21" s="118" t="n"/>
+      <c r="G21" s="118" t="n"/>
+      <c r="H21" s="119" t="n"/>
+      <c r="I21" s="86" t="n"/>
+      <c r="J21" s="86" t="n"/>
+      <c r="K21" s="86" t="n"/>
+      <c r="L21" s="86" t="n"/>
     </row>
     <row r="22" ht="20.1" customFormat="1" customHeight="1" s="4">
-      <c r="A22" s="70" t="inlineStr">
+      <c r="A22" s="120" t="inlineStr">
         <is>
           <t>İstek No</t>
         </is>
       </c>
-      <c r="B22" s="70" t="inlineStr">
+      <c r="B22" s="120" t="inlineStr">
         <is>
           <t>Teslim Tarihi</t>
         </is>
       </c>
-      <c r="C22" s="56" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="70" t="inlineStr">
+      <c r="C22" s="121" t="n"/>
+      <c r="D22" s="122" t="n"/>
+      <c r="E22" s="120" t="inlineStr">
         <is>
           <t>Teslimat</t>
         </is>
       </c>
-      <c r="F22" s="70" t="inlineStr">
+      <c r="F22" s="120" t="inlineStr">
         <is>
           <t>Teslimat Şekli</t>
         </is>
       </c>
-      <c r="G22" s="70" t="inlineStr">
+      <c r="G22" s="120" t="inlineStr">
         <is>
           <t>Ödeme Şekli</t>
         </is>
       </c>
-      <c r="H22" s="57" t="n"/>
+      <c r="H22" s="122" t="n"/>
+      <c r="I22" s="86" t="n"/>
+      <c r="J22" s="86" t="n"/>
+      <c r="K22" s="86" t="n"/>
+      <c r="L22" s="86" t="n"/>
     </row>
     <row r="23" ht="69.8" customFormat="1" customHeight="1" s="4">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="123" t="inlineStr">
         <is>
           <t>QBR2525</t>
         </is>
       </c>
-      <c r="B23" s="75" t="inlineStr">
+      <c r="B23" s="124" t="inlineStr">
         <is>
           <t>ANT-DVI-ENC-hfkaha - 29 adet T0+34 Hafta
 GSHG - 9 adet T0+12 Hafta
 T0: Sipariş Onay Tarihi</t>
         </is>
       </c>
-      <c r="C23" s="81" t="n"/>
-      <c r="D23" s="82" t="n"/>
-      <c r="E23" s="69" t="inlineStr">
+      <c r="C23" s="125" t="n"/>
+      <c r="D23" s="126" t="n"/>
+      <c r="E23" s="127" t="inlineStr">
         <is>
           <t>Yurtiçi Kargo</t>
         </is>
       </c>
-      <c r="F23" s="69" t="inlineStr">
+      <c r="F23" s="127" t="inlineStr">
         <is>
           <t>Kapı Teslim</t>
         </is>
       </c>
-      <c r="G23" s="69" t="inlineStr">
+      <c r="G23" s="127" t="inlineStr">
         <is>
           <t>Peşin</t>
         </is>
       </c>
-      <c r="H23" s="82" t="n"/>
+      <c r="H23" s="126" t="n"/>
+      <c r="I23" s="86" t="n"/>
+      <c r="J23" s="86" t="n"/>
+      <c r="K23" s="86" t="n"/>
+      <c r="L23" s="86" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="78">
-      <c r="A24" s="46" t="n"/>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="62" t="n"/>
-      <c r="F24" s="62" t="n"/>
-      <c r="G24" s="62" t="n"/>
-      <c r="H24" s="45" t="n"/>
+      <c r="A24" s="128" t="n"/>
+      <c r="B24" s="129" t="n"/>
+      <c r="C24" s="129" t="n"/>
+      <c r="D24" s="129" t="n"/>
+      <c r="E24" s="103" t="n"/>
+      <c r="F24" s="103" t="n"/>
+      <c r="G24" s="103" t="n"/>
+      <c r="H24" s="130" t="n"/>
+      <c r="I24" s="86" t="n"/>
+      <c r="J24" s="86" t="n"/>
+      <c r="K24" s="86" t="n"/>
+      <c r="L24" s="86" t="n"/>
     </row>
     <row r="25" ht="14.25" customHeight="1" s="78">
-      <c r="A25" s="47" t="n"/>
-      <c r="B25" s="62" t="n"/>
-      <c r="C25" s="62" t="n"/>
-      <c r="D25" s="62" t="n"/>
-      <c r="E25" s="62" t="n"/>
-      <c r="F25" s="62" t="n"/>
-      <c r="G25" s="62" t="n"/>
-      <c r="H25" s="28" t="n"/>
+      <c r="A25" s="131" t="n"/>
+      <c r="B25" s="103" t="n"/>
+      <c r="C25" s="103" t="n"/>
+      <c r="D25" s="103" t="n"/>
+      <c r="E25" s="103" t="n"/>
+      <c r="F25" s="103" t="n"/>
+      <c r="G25" s="103" t="n"/>
+      <c r="H25" s="119" t="n"/>
+      <c r="I25" s="86" t="n"/>
+      <c r="J25" s="86" t="n"/>
+      <c r="K25" s="86" t="n"/>
+      <c r="L25" s="86" t="n"/>
     </row>
     <row r="26" ht="15" customFormat="1" customHeight="1" s="4">
-      <c r="A26" s="70" t="inlineStr">
+      <c r="A26" s="120" t="inlineStr">
         <is>
           <t>Adet</t>
         </is>
       </c>
-      <c r="B26" s="70" t="inlineStr">
+      <c r="B26" s="120" t="inlineStr">
         <is>
           <t>Antsis Ürün Kodu</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="120" t="inlineStr">
         <is>
           <t>Açıklama</t>
         </is>
       </c>
-      <c r="D26" s="56" t="n"/>
-      <c r="E26" s="56" t="n"/>
-      <c r="F26" s="57" t="n"/>
-      <c r="G26" s="70" t="inlineStr">
+      <c r="D26" s="121" t="n"/>
+      <c r="E26" s="121" t="n"/>
+      <c r="F26" s="122" t="n"/>
+      <c r="G26" s="120" t="inlineStr">
         <is>
           <t>Birim Fiyat</t>
         </is>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="132" t="inlineStr">
         <is>
           <t>Toplam Fiyat</t>
         </is>
       </c>
+      <c r="I26" s="86" t="n"/>
+      <c r="J26" s="86" t="n"/>
+      <c r="K26" s="86" t="n"/>
+      <c r="L26" s="86" t="n"/>
     </row>
     <row r="27" ht="37.9" customFormat="1" customHeight="1" s="4">
-      <c r="A27" s="34" t="n">
+      <c r="A27" s="133" t="n">
         <v>29</v>
       </c>
-      <c r="B27" s="55" t="inlineStr">
+      <c r="B27" s="123" t="inlineStr">
         <is>
           <t>ANT-DVI-ENC-hfkaha</t>
         </is>
       </c>
-      <c r="C27" s="83" t="inlineStr">
+      <c r="C27" s="134" t="inlineStr">
         <is>
           <t>ali ata bak / 002525
 ( K ve P pizisyonlari fiyata dahil degildir. )</t>
         </is>
       </c>
-      <c r="D27" s="84" t="n"/>
-      <c r="E27" s="84" t="n"/>
-      <c r="F27" s="85" t="n"/>
-      <c r="G27" s="35" t="inlineStr">
+      <c r="D27" s="135" t="n"/>
+      <c r="E27" s="135" t="n"/>
+      <c r="F27" s="136" t="n"/>
+      <c r="G27" s="137" t="inlineStr">
         <is>
           <t>$10,00</t>
         </is>
       </c>
-      <c r="H27" s="35" t="inlineStr">
+      <c r="H27" s="137" t="inlineStr">
         <is>
           <t>$290,00</t>
         </is>
       </c>
+      <c r="I27" s="86" t="n"/>
+      <c r="J27" s="86" t="n"/>
+      <c r="K27" s="86" t="n"/>
+      <c r="L27" s="86" t="n"/>
     </row>
     <row r="28" ht="21.95" customFormat="1" customHeight="1" s="4">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="133" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="55" t="inlineStr">
+      <c r="B28" s="123" t="inlineStr">
         <is>
           <t>GSHG</t>
         </is>
       </c>
-      <c r="C28" s="83" t="inlineStr">
+      <c r="C28" s="134" t="inlineStr">
         <is>
           <t>test urun / 001111</t>
         </is>
       </c>
-      <c r="D28" s="84" t="n"/>
-      <c r="E28" s="84" t="n"/>
-      <c r="F28" s="85" t="n"/>
-      <c r="G28" s="35" t="inlineStr">
+      <c r="D28" s="135" t="n"/>
+      <c r="E28" s="135" t="n"/>
+      <c r="F28" s="136" t="n"/>
+      <c r="G28" s="137" t="inlineStr">
         <is>
           <t>$25,00</t>
         </is>
       </c>
-      <c r="H28" s="35" t="inlineStr">
+      <c r="H28" s="137" t="inlineStr">
         <is>
           <t>$225,00</t>
         </is>
       </c>
+      <c r="I28" s="86" t="n"/>
+      <c r="J28" s="86" t="n"/>
+      <c r="K28" s="86" t="n"/>
+      <c r="L28" s="86" t="n"/>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A29" s="36" t="n"/>
-      <c r="B29" s="37" t="n"/>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="38" t="n"/>
-      <c r="G29" s="39" t="inlineStr">
+      <c r="A29" s="138" t="n"/>
+      <c r="B29" s="139" t="n"/>
+      <c r="C29" s="139" t="n"/>
+      <c r="D29" s="139" t="n"/>
+      <c r="E29" s="139" t="n"/>
+      <c r="F29" s="140" t="n"/>
+      <c r="G29" s="141" t="inlineStr">
         <is>
           <t>Ara Toplam</t>
         </is>
       </c>
-      <c r="H29" s="40" t="inlineStr">
+      <c r="H29" s="142" t="inlineStr">
         <is>
           <t>$515,00</t>
         </is>
       </c>
+      <c r="I29" s="86" t="n"/>
+      <c r="J29" s="86" t="n"/>
+      <c r="K29" s="86" t="n"/>
+      <c r="L29" s="86" t="n"/>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="37" t="n"/>
-      <c r="C30" s="37" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="38" t="n"/>
-      <c r="G30" s="39" t="inlineStr">
+      <c r="A30" s="138" t="n"/>
+      <c r="B30" s="139" t="n"/>
+      <c r="C30" s="139" t="n"/>
+      <c r="D30" s="139" t="n"/>
+      <c r="E30" s="143" t="n"/>
+      <c r="F30" s="140" t="n"/>
+      <c r="G30" s="141" t="inlineStr">
         <is>
           <t>KDV (%20)</t>
         </is>
       </c>
-      <c r="H30" s="35" t="inlineStr">
+      <c r="H30" s="137" t="inlineStr">
         <is>
           <t>$103,00</t>
         </is>
       </c>
+      <c r="I30" s="86" t="n"/>
+      <c r="J30" s="86" t="n"/>
+      <c r="K30" s="86" t="n"/>
+      <c r="L30" s="86" t="n"/>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="4">
-      <c r="A31" s="41" t="n"/>
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="38" t="n"/>
-      <c r="E31" s="38" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="A31" s="144" t="n"/>
+      <c r="B31" s="140" t="n"/>
+      <c r="C31" s="140" t="n"/>
+      <c r="D31" s="140" t="n"/>
+      <c r="E31" s="140" t="n"/>
+      <c r="F31" s="143" t="n"/>
+      <c r="G31" s="145" t="inlineStr">
         <is>
           <t>Toplam</t>
         </is>
       </c>
-      <c r="H31" s="40" t="inlineStr">
+      <c r="H31" s="142" t="inlineStr">
         <is>
           <t>$618,00</t>
         </is>
       </c>
+      <c r="I31" s="86" t="n"/>
+      <c r="J31" s="86" t="n"/>
+      <c r="K31" s="86" t="n"/>
+      <c r="L31" s="86" t="n"/>
     </row>
     <row r="32" ht="20.1" customFormat="1" customHeight="1" s="4">
-      <c r="A32" s="41" t="n"/>
-      <c r="B32" s="38" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="38" t="n"/>
-      <c r="E32" s="38" t="n"/>
-      <c r="F32" s="38" t="n"/>
-      <c r="G32" s="38" t="n"/>
-      <c r="H32" s="43" t="n"/>
+      <c r="A32" s="144" t="n"/>
+      <c r="B32" s="140" t="n"/>
+      <c r="C32" s="140" t="n"/>
+      <c r="D32" s="140" t="n"/>
+      <c r="E32" s="140" t="n"/>
+      <c r="F32" s="140" t="n"/>
+      <c r="G32" s="140" t="n"/>
+      <c r="H32" s="146" t="n"/>
+      <c r="I32" s="86" t="n"/>
+      <c r="J32" s="86" t="n"/>
+      <c r="K32" s="86" t="n"/>
+      <c r="L32" s="86" t="n"/>
     </row>
     <row r="33" ht="20.1" customFormat="1" customHeight="1" s="4">
-      <c r="A33" s="71" t="inlineStr">
+      <c r="A33" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">Teklif isteğiniz için teşekkürler. Teklif ile alakalı her türlü sorunuz için lütfen bizimle iletişime geçiniz. </t>
         </is>
       </c>
-      <c r="B33" s="62" t="n"/>
-      <c r="C33" s="62" t="n"/>
-      <c r="D33" s="62" t="n"/>
-      <c r="E33" s="62" t="n"/>
-      <c r="F33" s="62" t="n"/>
-      <c r="G33" s="62" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="72" t="n"/>
+      <c r="B33" s="103" t="n"/>
+      <c r="C33" s="103" t="n"/>
+      <c r="D33" s="103" t="n"/>
+      <c r="E33" s="103" t="n"/>
+      <c r="F33" s="103" t="n"/>
+      <c r="G33" s="103" t="n"/>
+      <c r="H33" s="104" t="n"/>
+      <c r="I33" s="147" t="n"/>
+      <c r="J33" s="86" t="n"/>
+      <c r="K33" s="86" t="n"/>
+      <c r="L33" s="86" t="n"/>
     </row>
     <row r="34" ht="9.6" customFormat="1" customHeight="1" s="4">
-      <c r="A34" s="44" t="n"/>
-      <c r="B34" s="21" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="A34" s="148" t="n"/>
+      <c r="B34" s="108" t="n"/>
+      <c r="C34" s="108" t="n"/>
+      <c r="D34" s="108" t="n"/>
+      <c r="E34" s="108" t="n"/>
+      <c r="F34" s="108" t="n"/>
+      <c r="G34" s="108" t="n"/>
+      <c r="H34" s="113" t="n"/>
+      <c r="I34" s="149" t="n"/>
+      <c r="J34" s="86" t="n"/>
+      <c r="K34" s="86" t="n"/>
+      <c r="L34" s="86" t="n"/>
     </row>
     <row r="35" ht="14.1" customFormat="1" customHeight="1" s="4">
-      <c r="A35" s="53" t="inlineStr">
+      <c r="A35" s="150" t="inlineStr">
         <is>
           <t>Şartlar:</t>
         </is>
       </c>
-      <c r="B35" s="38" t="n"/>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="38" t="n"/>
-      <c r="E35" s="38" t="n"/>
-      <c r="F35" s="38" t="n"/>
-      <c r="G35" s="38" t="n"/>
-      <c r="H35" s="43" t="n"/>
-    </row>
-    <row r="36" ht="37.9" customFormat="1" customHeight="1" s="4">
-      <c r="A36" s="86" t="inlineStr">
+      <c r="B35" s="140" t="n"/>
+      <c r="C35" s="140" t="n"/>
+      <c r="D35" s="140" t="n"/>
+      <c r="E35" s="140" t="n"/>
+      <c r="F35" s="140" t="n"/>
+      <c r="G35" s="140" t="n"/>
+      <c r="H35" s="146" t="n"/>
+      <c r="I35" s="86" t="n"/>
+      <c r="J35" s="86" t="n"/>
+      <c r="K35" s="86" t="n"/>
+      <c r="L35" s="86" t="n"/>
+    </row>
+    <row r="36" ht="14.1" customFormat="1" customHeight="1" s="4">
+      <c r="A36" s="151" t="inlineStr">
         <is>
           <t>ANT-DVI-ENC-hfkaha, GSHG</t>
         </is>
       </c>
-      <c r="B36" s="38" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="38" t="n"/>
-      <c r="E36" s="38" t="n"/>
-      <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n"/>
-      <c r="H36" s="43" t="n"/>
-    </row>
-    <row r="37" ht="21.95" customFormat="1" customHeight="1" s="4">
-      <c r="A37" s="86" t="inlineStr">
+      <c r="B36" s="140" t="n"/>
+      <c r="C36" s="140" t="n"/>
+      <c r="D36" s="140" t="n"/>
+      <c r="E36" s="140" t="n"/>
+      <c r="F36" s="140" t="n"/>
+      <c r="G36" s="140" t="n"/>
+      <c r="H36" s="146" t="n"/>
+      <c r="I36" s="86" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="86" t="n"/>
+      <c r="L36" s="86" t="n"/>
+    </row>
+    <row r="37" ht="14.1" customFormat="1" customHeight="1" s="4">
+      <c r="A37" s="151" t="inlineStr">
         <is>
           <t>Ozel sart A</t>
         </is>
       </c>
-      <c r="B37" s="38" t="n"/>
-      <c r="C37" s="38" t="n"/>
-      <c r="D37" s="38" t="n"/>
-      <c r="E37" s="38" t="n"/>
-      <c r="F37" s="38" t="n"/>
-      <c r="G37" s="38" t="n"/>
-      <c r="H37" s="43" t="n"/>
-    </row>
-    <row r="38" ht="85.75" customFormat="1" customHeight="1" s="4">
-      <c r="A38" s="86" t="inlineStr">
+      <c r="B37" s="140" t="n"/>
+      <c r="C37" s="140" t="n"/>
+      <c r="D37" s="140" t="n"/>
+      <c r="E37" s="140" t="n"/>
+      <c r="F37" s="140" t="n"/>
+      <c r="G37" s="140" t="n"/>
+      <c r="H37" s="146" t="n"/>
+      <c r="I37" s="86" t="n"/>
+      <c r="J37" s="86" t="n"/>
+      <c r="K37" s="86" t="n"/>
+      <c r="L37" s="86" t="n"/>
+    </row>
+    <row r="38" ht="14.1" customFormat="1" customHeight="1" s="4">
+      <c r="A38" s="151" t="inlineStr">
         <is>
           <t>Teklif edilen ürünler rafta hazır olarak üretilmektedir.</t>
         </is>
       </c>
-      <c r="B38" s="62" t="n"/>
-      <c r="C38" s="62" t="n"/>
-      <c r="D38" s="62" t="n"/>
-      <c r="E38" s="62" t="n"/>
-      <c r="F38" s="62" t="n"/>
-      <c r="G38" s="62" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="72" t="n"/>
-    </row>
-    <row r="39" ht="133.6" customFormat="1" customHeight="1" s="4">
-      <c r="A39" s="86" t="inlineStr">
+      <c r="B38" s="103" t="n"/>
+      <c r="C38" s="103" t="n"/>
+      <c r="D38" s="103" t="n"/>
+      <c r="E38" s="103" t="n"/>
+      <c r="F38" s="103" t="n"/>
+      <c r="G38" s="103" t="n"/>
+      <c r="H38" s="104" t="n"/>
+      <c r="I38" s="147" t="n"/>
+      <c r="J38" s="86" t="n"/>
+      <c r="K38" s="86" t="n"/>
+      <c r="L38" s="86" t="n"/>
+    </row>
+    <row r="39" ht="14.1" customFormat="1" customHeight="1" s="4">
+      <c r="A39" s="151" t="inlineStr">
         <is>
           <t>Teklif isteğinde belirtilen şartnameye veya teknik resme uygunluğu satın alanın sorumluluğundadır.</t>
         </is>
       </c>
-      <c r="B39" s="62" t="n"/>
-      <c r="C39" s="62" t="n"/>
-      <c r="D39" s="62" t="n"/>
-      <c r="E39" s="62" t="n"/>
-      <c r="F39" s="62" t="n"/>
-      <c r="G39" s="62" t="n"/>
-      <c r="H39" s="17" t="n"/>
-      <c r="I39" s="72" t="n"/>
-    </row>
-    <row r="40" ht="101.7" customFormat="1" customHeight="1" s="4">
-      <c r="A40" s="86" t="inlineStr">
+      <c r="B39" s="103" t="n"/>
+      <c r="C39" s="103" t="n"/>
+      <c r="D39" s="103" t="n"/>
+      <c r="E39" s="103" t="n"/>
+      <c r="F39" s="103" t="n"/>
+      <c r="G39" s="103" t="n"/>
+      <c r="H39" s="104" t="n"/>
+      <c r="I39" s="147" t="n"/>
+      <c r="J39" s="86" t="n"/>
+      <c r="K39" s="86" t="n"/>
+      <c r="L39" s="86" t="n"/>
+    </row>
+    <row r="40" ht="14.1" customFormat="1" customHeight="1" s="4">
+      <c r="A40" s="151" t="inlineStr">
         <is>
           <t>Sistemde kullanılacak kablonun tarafınızdan tedarik edilceği varsayılmıştır.</t>
         </is>
       </c>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
-      <c r="H40" s="43" t="n"/>
-    </row>
-    <row r="41" ht="149.55" customHeight="1" s="78">
-      <c r="A41" s="86" t="inlineStr">
+      <c r="B40" s="140" t="n"/>
+      <c r="C40" s="140" t="n"/>
+      <c r="D40" s="140" t="n"/>
+      <c r="E40" s="140" t="n"/>
+      <c r="F40" s="140" t="n"/>
+      <c r="G40" s="140" t="n"/>
+      <c r="H40" s="146" t="n"/>
+      <c r="I40" s="86" t="n"/>
+      <c r="J40" s="86" t="n"/>
+      <c r="K40" s="86" t="n"/>
+      <c r="L40" s="86" t="n"/>
+    </row>
+    <row r="41" ht="14.1" customHeight="1" s="78">
+      <c r="A41" s="151" t="inlineStr">
         <is>
           <t>Ürünler için sipariş numarası, üretici adı, parça kodu, seri numarası yazılı CoC belgesi ve test raporu verilecektir.</t>
         </is>
       </c>
-      <c r="B41" s="62" t="n"/>
-      <c r="C41" s="62" t="n"/>
-      <c r="D41" s="62" t="n"/>
-      <c r="E41" s="62" t="n"/>
-      <c r="F41" s="62" t="n"/>
-      <c r="G41" s="62" t="n"/>
-      <c r="H41" s="17" t="n"/>
-    </row>
-    <row r="42" ht="133.6" customHeight="1" s="78">
-      <c r="A42" s="86" t="inlineStr">
+      <c r="B41" s="103" t="n"/>
+      <c r="C41" s="103" t="n"/>
+      <c r="D41" s="103" t="n"/>
+      <c r="E41" s="103" t="n"/>
+      <c r="F41" s="103" t="n"/>
+      <c r="G41" s="103" t="n"/>
+      <c r="H41" s="104" t="n"/>
+      <c r="I41" s="86" t="n"/>
+      <c r="J41" s="86" t="n"/>
+      <c r="K41" s="86" t="n"/>
+      <c r="L41" s="86" t="n"/>
+    </row>
+    <row r="42" ht="14.1" customHeight="1" s="78">
+      <c r="A42" s="151" t="inlineStr">
         <is>
           <t>Teklif çevresel testlerin bünyenizde ve bedelsiz olarak yapılacağı varsayılarak hazırlanmıştır.</t>
         </is>
       </c>
-      <c r="B42" s="62" t="n"/>
-      <c r="C42" s="62" t="n"/>
-      <c r="D42" s="62" t="n"/>
-      <c r="E42" s="62" t="n"/>
-      <c r="F42" s="62" t="n"/>
-      <c r="G42" s="62" t="n"/>
-      <c r="H42" s="17" t="n"/>
-    </row>
-    <row r="43" ht="149.55" customHeight="1" s="78">
-      <c r="A43" s="86" t="inlineStr">
+      <c r="B42" s="103" t="n"/>
+      <c r="C42" s="103" t="n"/>
+      <c r="D42" s="103" t="n"/>
+      <c r="E42" s="103" t="n"/>
+      <c r="F42" s="103" t="n"/>
+      <c r="G42" s="103" t="n"/>
+      <c r="H42" s="104" t="n"/>
+      <c r="I42" s="86" t="n"/>
+      <c r="J42" s="86" t="n"/>
+      <c r="K42" s="86" t="n"/>
+      <c r="L42" s="86" t="n"/>
+    </row>
+    <row r="43" ht="14.1" customHeight="1" s="78">
+      <c r="A43" s="151" t="inlineStr">
         <is>
           <t>Genel hüküm ve şartlar "https://antsiselektronik.com.tr/wp-content/uploads/2024/12/" adresinden indirilebilir.</t>
         </is>
       </c>
-      <c r="B43" s="38" t="n"/>
-      <c r="C43" s="38" t="n"/>
-      <c r="D43" s="38" t="n"/>
-      <c r="E43" s="38" t="n"/>
-      <c r="F43" s="38" t="n"/>
-      <c r="G43" s="38" t="n"/>
-      <c r="H43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="85.75" customHeight="1" s="78">
-      <c r="A44" s="86" t="inlineStr">
+      <c r="B43" s="140" t="n"/>
+      <c r="C43" s="140" t="n"/>
+      <c r="D43" s="140" t="n"/>
+      <c r="E43" s="140" t="n"/>
+      <c r="F43" s="140" t="n"/>
+      <c r="G43" s="140" t="n"/>
+      <c r="H43" s="146" t="n"/>
+      <c r="I43" s="86" t="n"/>
+      <c r="J43" s="86" t="n"/>
+      <c r="K43" s="86" t="n"/>
+      <c r="L43" s="86" t="n"/>
+    </row>
+    <row r="44" ht="14.1" customHeight="1" s="78">
+      <c r="A44" s="151" t="inlineStr">
         <is>
           <t>Ürünlerin faturası, ürünlerin sevkiyatına mütakip kesilecektir.</t>
         </is>
       </c>
-      <c r="B44" s="38" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="38" t="n"/>
-      <c r="F44" s="38" t="n"/>
-      <c r="G44" s="38" t="n"/>
-      <c r="H44" s="43" t="n"/>
+      <c r="B44" s="140" t="n"/>
+      <c r="C44" s="140" t="n"/>
+      <c r="D44" s="140" t="n"/>
+      <c r="E44" s="140" t="n"/>
+      <c r="F44" s="140" t="n"/>
+      <c r="G44" s="140" t="n"/>
+      <c r="H44" s="146" t="n"/>
+      <c r="I44" s="86" t="n"/>
+      <c r="J44" s="86" t="n"/>
+      <c r="K44" s="86" t="n"/>
+      <c r="L44" s="86" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="71" t="n"/>
-      <c r="B45" s="62" t="n"/>
-      <c r="C45" s="62" t="n"/>
-      <c r="D45" s="62" t="n"/>
-      <c r="E45" s="62" t="n"/>
-      <c r="F45" s="62" t="n"/>
-      <c r="G45" s="62" t="n"/>
-      <c r="H45" s="17" t="n"/>
+      <c r="A45" s="105" t="n"/>
+      <c r="B45" s="103" t="n"/>
+      <c r="C45" s="103" t="n"/>
+      <c r="D45" s="103" t="n"/>
+      <c r="E45" s="103" t="n"/>
+      <c r="F45" s="103" t="n"/>
+      <c r="G45" s="103" t="n"/>
+      <c r="H45" s="104" t="n"/>
+      <c r="I45" s="86" t="n"/>
+      <c r="J45" s="86" t="n"/>
+      <c r="K45" s="86" t="n"/>
+      <c r="L45" s="86" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="71" t="n"/>
-      <c r="B46" s="62" t="n"/>
-      <c r="C46" s="62" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="62" t="n"/>
-      <c r="F46" s="62" t="n"/>
-      <c r="G46" s="62" t="n"/>
-      <c r="H46" s="17" t="n"/>
+      <c r="A46" s="105" t="n"/>
+      <c r="B46" s="103" t="n"/>
+      <c r="C46" s="103" t="n"/>
+      <c r="D46" s="103" t="n"/>
+      <c r="E46" s="103" t="n"/>
+      <c r="F46" s="103" t="n"/>
+      <c r="G46" s="103" t="n"/>
+      <c r="H46" s="104" t="n"/>
+      <c r="I46" s="86" t="n"/>
+      <c r="J46" s="86" t="n"/>
+      <c r="K46" s="86" t="n"/>
+      <c r="L46" s="86" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="n"/>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n"/>
-      <c r="G47" s="15" t="n"/>
-      <c r="H47" s="16" t="n"/>
-    </row>
-    <row r="48"/>
+      <c r="A47" s="152" t="n"/>
+      <c r="B47" s="153" t="n"/>
+      <c r="C47" s="153" t="n"/>
+      <c r="D47" s="153" t="n"/>
+      <c r="E47" s="153" t="n"/>
+      <c r="F47" s="153" t="n"/>
+      <c r="G47" s="153" t="n"/>
+      <c r="H47" s="154" t="n"/>
+      <c r="I47" s="86" t="n"/>
+      <c r="J47" s="86" t="n"/>
+      <c r="K47" s="86" t="n"/>
+      <c r="L47" s="86" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="86" t="n"/>
+      <c r="B48" s="86" t="n"/>
+      <c r="C48" s="86" t="n"/>
+      <c r="D48" s="86" t="n"/>
+      <c r="E48" s="86" t="n"/>
+      <c r="F48" s="86" t="n"/>
+      <c r="G48" s="86" t="n"/>
+      <c r="H48" s="86" t="n"/>
+      <c r="I48" s="86" t="n"/>
+      <c r="J48" s="86" t="n"/>
+      <c r="K48" s="86" t="n"/>
+      <c r="L48" s="86" t="n"/>
+    </row>
     <row r="49">
-      <c r="B49" s="54" t="n"/>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
+      <c r="A49" s="86" t="n"/>
+      <c r="B49" s="155" t="n"/>
+      <c r="C49" s="86" t="n"/>
+      <c r="D49" s="86" t="n"/>
+      <c r="E49" s="86" t="n"/>
+      <c r="F49" s="86" t="n"/>
+      <c r="G49" s="86" t="n"/>
+      <c r="H49" s="86" t="n"/>
+      <c r="I49" s="86" t="n"/>
+      <c r="J49" s="86" t="n"/>
+      <c r="K49" s="86" t="n"/>
+      <c r="L49" s="86" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="86" t="n"/>
+      <c r="B50" s="86" t="n"/>
+      <c r="C50" s="86" t="n"/>
+      <c r="D50" s="86" t="n"/>
+      <c r="E50" s="86" t="n"/>
+      <c r="F50" s="86" t="n"/>
+      <c r="G50" s="86" t="n"/>
+      <c r="H50" s="86" t="n"/>
+      <c r="I50" s="86" t="n"/>
+      <c r="J50" s="86" t="n"/>
+      <c r="K50" s="86" t="n"/>
+      <c r="L50" s="86" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="86" t="n"/>
+      <c r="B51" s="86" t="n"/>
+      <c r="C51" s="86" t="n"/>
+      <c r="D51" s="86" t="n"/>
+      <c r="E51" s="86" t="n"/>
+      <c r="F51" s="86" t="n"/>
+      <c r="G51" s="86" t="n"/>
+      <c r="H51" s="86" t="n"/>
+      <c r="I51" s="86" t="n"/>
+      <c r="J51" s="86" t="n"/>
+      <c r="K51" s="86" t="n"/>
+      <c r="L51" s="86" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="86" t="n"/>
+      <c r="B52" s="86" t="n"/>
+      <c r="C52" s="86" t="n"/>
+      <c r="D52" s="86" t="n"/>
+      <c r="E52" s="86" t="n"/>
+      <c r="F52" s="86" t="n"/>
+      <c r="G52" s="86" t="n"/>
+      <c r="H52" s="86" t="n"/>
+      <c r="I52" s="86" t="n"/>
+      <c r="J52" s="86" t="n"/>
+      <c r="K52" s="86" t="n"/>
+      <c r="L52" s="86" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="86" t="n"/>
+      <c r="B53" s="86" t="n"/>
+      <c r="C53" s="86" t="n"/>
+      <c r="D53" s="86" t="n"/>
+      <c r="E53" s="86" t="n"/>
+      <c r="F53" s="86" t="n"/>
+      <c r="G53" s="86" t="n"/>
+      <c r="H53" s="86" t="n"/>
+      <c r="I53" s="86" t="n"/>
+      <c r="J53" s="86" t="n"/>
+      <c r="K53" s="86" t="n"/>
+      <c r="L53" s="86" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="86" t="n"/>
+      <c r="B54" s="86" t="n"/>
+      <c r="C54" s="86" t="n"/>
+      <c r="D54" s="86" t="n"/>
+      <c r="E54" s="86" t="n"/>
+      <c r="F54" s="86" t="n"/>
+      <c r="G54" s="86" t="n"/>
+      <c r="H54" s="86" t="n"/>
+      <c r="I54" s="86" t="n"/>
+      <c r="J54" s="86" t="n"/>
+      <c r="K54" s="86" t="n"/>
+      <c r="L54" s="86" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="86" t="n"/>
+      <c r="B55" s="86" t="n"/>
+      <c r="C55" s="86" t="n"/>
+      <c r="D55" s="86" t="n"/>
+      <c r="E55" s="86" t="n"/>
+      <c r="F55" s="86" t="n"/>
+      <c r="G55" s="86" t="n"/>
+      <c r="H55" s="86" t="n"/>
+      <c r="I55" s="86" t="n"/>
+      <c r="J55" s="86" t="n"/>
+      <c r="K55" s="86" t="n"/>
+      <c r="L55" s="86" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="86" t="n"/>
+      <c r="B56" s="86" t="n"/>
+      <c r="C56" s="86" t="n"/>
+      <c r="D56" s="86" t="n"/>
+      <c r="E56" s="86" t="n"/>
+      <c r="F56" s="86" t="n"/>
+      <c r="G56" s="86" t="n"/>
+      <c r="H56" s="86" t="n"/>
+      <c r="I56" s="86" t="n"/>
+      <c r="J56" s="86" t="n"/>
+      <c r="K56" s="86" t="n"/>
+      <c r="L56" s="86" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="86" t="n"/>
+      <c r="B57" s="86" t="n"/>
+      <c r="C57" s="86" t="n"/>
+      <c r="D57" s="86" t="n"/>
+      <c r="E57" s="86" t="n"/>
+      <c r="F57" s="86" t="n"/>
+      <c r="G57" s="86" t="n"/>
+      <c r="H57" s="86" t="n"/>
+      <c r="I57" s="86" t="n"/>
+      <c r="J57" s="86" t="n"/>
+      <c r="K57" s="86" t="n"/>
+      <c r="L57" s="86" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="86" t="n"/>
+      <c r="B58" s="86" t="n"/>
+      <c r="C58" s="86" t="n"/>
+      <c r="D58" s="86" t="n"/>
+      <c r="E58" s="86" t="n"/>
+      <c r="F58" s="86" t="n"/>
+      <c r="G58" s="86" t="n"/>
+      <c r="H58" s="86" t="n"/>
+      <c r="I58" s="86" t="n"/>
+      <c r="J58" s="86" t="n"/>
+      <c r="K58" s="86" t="n"/>
+      <c r="L58" s="86" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="86" t="n"/>
+      <c r="B59" s="86" t="n"/>
+      <c r="C59" s="86" t="n"/>
+      <c r="D59" s="86" t="n"/>
+      <c r="E59" s="86" t="n"/>
+      <c r="F59" s="86" t="n"/>
+      <c r="G59" s="86" t="n"/>
+      <c r="H59" s="86" t="n"/>
+      <c r="I59" s="86" t="n"/>
+      <c r="J59" s="86" t="n"/>
+      <c r="K59" s="86" t="n"/>
+      <c r="L59" s="86" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="86" t="n"/>
+      <c r="B60" s="86" t="n"/>
+      <c r="C60" s="86" t="n"/>
+      <c r="D60" s="86" t="n"/>
+      <c r="E60" s="86" t="n"/>
+      <c r="F60" s="86" t="n"/>
+      <c r="G60" s="86" t="n"/>
+      <c r="H60" s="86" t="n"/>
+      <c r="I60" s="86" t="n"/>
+      <c r="J60" s="86" t="n"/>
+      <c r="K60" s="86" t="n"/>
+      <c r="L60" s="86" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="86" t="n"/>
+      <c r="B61" s="86" t="n"/>
+      <c r="C61" s="86" t="n"/>
+      <c r="D61" s="86" t="n"/>
+      <c r="E61" s="86" t="n"/>
+      <c r="F61" s="86" t="n"/>
+      <c r="G61" s="86" t="n"/>
+      <c r="H61" s="86" t="n"/>
+      <c r="I61" s="86" t="n"/>
+      <c r="J61" s="86" t="n"/>
+      <c r="K61" s="86" t="n"/>
+      <c r="L61" s="86" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="86" t="n"/>
+      <c r="B62" s="86" t="n"/>
+      <c r="C62" s="86" t="n"/>
+      <c r="D62" s="86" t="n"/>
+      <c r="E62" s="86" t="n"/>
+      <c r="F62" s="86" t="n"/>
+      <c r="G62" s="86" t="n"/>
+      <c r="H62" s="86" t="n"/>
+      <c r="I62" s="86" t="n"/>
+      <c r="J62" s="86" t="n"/>
+      <c r="K62" s="86" t="n"/>
+      <c r="L62" s="86" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="86" t="n"/>
+      <c r="B63" s="86" t="n"/>
+      <c r="C63" s="86" t="n"/>
+      <c r="D63" s="86" t="n"/>
+      <c r="E63" s="86" t="n"/>
+      <c r="F63" s="86" t="n"/>
+      <c r="G63" s="86" t="n"/>
+      <c r="H63" s="86" t="n"/>
+      <c r="I63" s="86" t="n"/>
+      <c r="J63" s="86" t="n"/>
+      <c r="K63" s="86" t="n"/>
+      <c r="L63" s="86" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="86" t="n"/>
+      <c r="B64" s="86" t="n"/>
+      <c r="C64" s="86" t="n"/>
+      <c r="D64" s="86" t="n"/>
+      <c r="E64" s="86" t="n"/>
+      <c r="F64" s="86" t="n"/>
+      <c r="G64" s="86" t="n"/>
+      <c r="H64" s="86" t="n"/>
+      <c r="I64" s="86" t="n"/>
+      <c r="J64" s="86" t="n"/>
+      <c r="K64" s="86" t="n"/>
+      <c r="L64" s="86" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="86" t="n"/>
+      <c r="B65" s="86" t="n"/>
+      <c r="C65" s="86" t="n"/>
+      <c r="D65" s="86" t="n"/>
+      <c r="E65" s="86" t="n"/>
+      <c r="F65" s="86" t="n"/>
+      <c r="G65" s="86" t="n"/>
+      <c r="H65" s="86" t="n"/>
+      <c r="I65" s="86" t="n"/>
+      <c r="J65" s="86" t="n"/>
+      <c r="K65" s="86" t="n"/>
+      <c r="L65" s="86" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="86" t="n"/>
+      <c r="B66" s="86" t="n"/>
+      <c r="C66" s="86" t="n"/>
+      <c r="D66" s="86" t="n"/>
+      <c r="E66" s="86" t="n"/>
+      <c r="F66" s="86" t="n"/>
+      <c r="G66" s="86" t="n"/>
+      <c r="H66" s="86" t="n"/>
+      <c r="I66" s="86" t="n"/>
+      <c r="J66" s="86" t="n"/>
+      <c r="K66" s="86" t="n"/>
+      <c r="L66" s="86" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="86" t="n"/>
+      <c r="B67" s="86" t="n"/>
+      <c r="C67" s="86" t="n"/>
+      <c r="D67" s="86" t="n"/>
+      <c r="E67" s="86" t="n"/>
+      <c r="F67" s="86" t="n"/>
+      <c r="G67" s="86" t="n"/>
+      <c r="H67" s="86" t="n"/>
+      <c r="I67" s="86" t="n"/>
+      <c r="J67" s="86" t="n"/>
+      <c r="K67" s="86" t="n"/>
+      <c r="L67" s="86" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="86" t="n"/>
+      <c r="B68" s="86" t="n"/>
+      <c r="C68" s="86" t="n"/>
+      <c r="D68" s="86" t="n"/>
+      <c r="E68" s="86" t="n"/>
+      <c r="F68" s="86" t="n"/>
+      <c r="G68" s="86" t="n"/>
+      <c r="H68" s="86" t="n"/>
+      <c r="I68" s="86" t="n"/>
+      <c r="J68" s="86" t="n"/>
+      <c r="K68" s="86" t="n"/>
+      <c r="L68" s="86" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="86" t="n"/>
+      <c r="B69" s="86" t="n"/>
+      <c r="C69" s="86" t="n"/>
+      <c r="D69" s="86" t="n"/>
+      <c r="E69" s="86" t="n"/>
+      <c r="F69" s="86" t="n"/>
+      <c r="G69" s="86" t="n"/>
+      <c r="H69" s="86" t="n"/>
+      <c r="I69" s="86" t="n"/>
+      <c r="J69" s="86" t="n"/>
+      <c r="K69" s="86" t="n"/>
+      <c r="L69" s="86" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="86" t="n"/>
+      <c r="B70" s="86" t="n"/>
+      <c r="C70" s="86" t="n"/>
+      <c r="D70" s="86" t="n"/>
+      <c r="E70" s="86" t="n"/>
+      <c r="F70" s="86" t="n"/>
+      <c r="G70" s="86" t="n"/>
+      <c r="H70" s="86" t="n"/>
+      <c r="I70" s="86" t="n"/>
+      <c r="J70" s="86" t="n"/>
+      <c r="K70" s="86" t="n"/>
+      <c r="L70" s="86" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="86" t="n"/>
+      <c r="B71" s="86" t="n"/>
+      <c r="C71" s="86" t="n"/>
+      <c r="D71" s="86" t="n"/>
+      <c r="E71" s="86" t="n"/>
+      <c r="F71" s="86" t="n"/>
+      <c r="G71" s="86" t="n"/>
+      <c r="H71" s="86" t="n"/>
+      <c r="I71" s="86" t="n"/>
+      <c r="J71" s="86" t="n"/>
+      <c r="K71" s="86" t="n"/>
+      <c r="L71" s="86" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="86" t="n"/>
+      <c r="B72" s="86" t="n"/>
+      <c r="C72" s="86" t="n"/>
+      <c r="D72" s="86" t="n"/>
+      <c r="E72" s="86" t="n"/>
+      <c r="F72" s="86" t="n"/>
+      <c r="G72" s="86" t="n"/>
+      <c r="H72" s="86" t="n"/>
+      <c r="I72" s="86" t="n"/>
+      <c r="J72" s="86" t="n"/>
+      <c r="K72" s="86" t="n"/>
+      <c r="L72" s="86" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="86" t="n"/>
+      <c r="B73" s="86" t="n"/>
+      <c r="C73" s="86" t="n"/>
+      <c r="D73" s="86" t="n"/>
+      <c r="E73" s="86" t="n"/>
+      <c r="F73" s="86" t="n"/>
+      <c r="G73" s="86" t="n"/>
+      <c r="H73" s="86" t="n"/>
+      <c r="I73" s="86" t="n"/>
+      <c r="J73" s="86" t="n"/>
+      <c r="K73" s="86" t="n"/>
+      <c r="L73" s="86" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="86" t="n"/>
+      <c r="B74" s="86" t="n"/>
+      <c r="C74" s="86" t="n"/>
+      <c r="D74" s="86" t="n"/>
+      <c r="E74" s="86" t="n"/>
+      <c r="F74" s="86" t="n"/>
+      <c r="G74" s="86" t="n"/>
+      <c r="H74" s="86" t="n"/>
+      <c r="I74" s="86" t="n"/>
+      <c r="J74" s="86" t="n"/>
+      <c r="K74" s="86" t="n"/>
+      <c r="L74" s="86" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="86" t="n"/>
+      <c r="B75" s="86" t="n"/>
+      <c r="C75" s="86" t="n"/>
+      <c r="D75" s="86" t="n"/>
+      <c r="E75" s="86" t="n"/>
+      <c r="F75" s="86" t="n"/>
+      <c r="G75" s="86" t="n"/>
+      <c r="H75" s="86" t="n"/>
+      <c r="I75" s="86" t="n"/>
+      <c r="J75" s="86" t="n"/>
+      <c r="K75" s="86" t="n"/>
+      <c r="L75" s="86" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="86" t="n"/>
+      <c r="B76" s="86" t="n"/>
+      <c r="C76" s="86" t="n"/>
+      <c r="D76" s="86" t="n"/>
+      <c r="E76" s="86" t="n"/>
+      <c r="F76" s="86" t="n"/>
+      <c r="G76" s="86" t="n"/>
+      <c r="H76" s="86" t="n"/>
+      <c r="I76" s="86" t="n"/>
+      <c r="J76" s="86" t="n"/>
+      <c r="K76" s="86" t="n"/>
+      <c r="L76" s="86" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="86" t="n"/>
+      <c r="B77" s="86" t="n"/>
+      <c r="C77" s="86" t="n"/>
+      <c r="D77" s="86" t="n"/>
+      <c r="E77" s="86" t="n"/>
+      <c r="F77" s="86" t="n"/>
+      <c r="G77" s="86" t="n"/>
+      <c r="H77" s="86" t="n"/>
+      <c r="I77" s="86" t="n"/>
+      <c r="J77" s="86" t="n"/>
+      <c r="K77" s="86" t="n"/>
+      <c r="L77" s="86" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="86" t="n"/>
+      <c r="B78" s="86" t="n"/>
+      <c r="C78" s="86" t="n"/>
+      <c r="D78" s="86" t="n"/>
+      <c r="E78" s="86" t="n"/>
+      <c r="F78" s="86" t="n"/>
+      <c r="G78" s="86" t="n"/>
+      <c r="H78" s="86" t="n"/>
+      <c r="I78" s="86" t="n"/>
+      <c r="J78" s="86" t="n"/>
+      <c r="K78" s="86" t="n"/>
+      <c r="L78" s="86" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="86" t="n"/>
+      <c r="B79" s="86" t="n"/>
+      <c r="C79" s="86" t="n"/>
+      <c r="D79" s="86" t="n"/>
+      <c r="E79" s="86" t="n"/>
+      <c r="F79" s="86" t="n"/>
+      <c r="G79" s="86" t="n"/>
+      <c r="H79" s="86" t="n"/>
+      <c r="I79" s="86" t="n"/>
+      <c r="J79" s="86" t="n"/>
+      <c r="K79" s="86" t="n"/>
+      <c r="L79" s="86" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="86" t="n"/>
+      <c r="B80" s="86" t="n"/>
+      <c r="C80" s="86" t="n"/>
+      <c r="D80" s="86" t="n"/>
+      <c r="E80" s="86" t="n"/>
+      <c r="F80" s="86" t="n"/>
+      <c r="G80" s="86" t="n"/>
+      <c r="H80" s="86" t="n"/>
+      <c r="I80" s="86" t="n"/>
+      <c r="J80" s="86" t="n"/>
+      <c r="K80" s="86" t="n"/>
+      <c r="L80" s="86" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="86" t="n"/>
+      <c r="B81" s="86" t="n"/>
+      <c r="C81" s="86" t="n"/>
+      <c r="D81" s="86" t="n"/>
+      <c r="E81" s="86" t="n"/>
+      <c r="F81" s="86" t="n"/>
+      <c r="G81" s="86" t="n"/>
+      <c r="H81" s="86" t="n"/>
+      <c r="I81" s="86" t="n"/>
+      <c r="J81" s="86" t="n"/>
+      <c r="K81" s="86" t="n"/>
+      <c r="L81" s="86" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="86" t="n"/>
+      <c r="B82" s="86" t="n"/>
+      <c r="C82" s="86" t="n"/>
+      <c r="D82" s="86" t="n"/>
+      <c r="E82" s="86" t="n"/>
+      <c r="F82" s="86" t="n"/>
+      <c r="G82" s="86" t="n"/>
+      <c r="H82" s="86" t="n"/>
+      <c r="I82" s="86" t="n"/>
+      <c r="J82" s="86" t="n"/>
+      <c r="K82" s="86" t="n"/>
+      <c r="L82" s="86" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="86" t="n"/>
+      <c r="B83" s="86" t="n"/>
+      <c r="C83" s="86" t="n"/>
+      <c r="D83" s="86" t="n"/>
+      <c r="E83" s="86" t="n"/>
+      <c r="F83" s="86" t="n"/>
+      <c r="G83" s="86" t="n"/>
+      <c r="H83" s="86" t="n"/>
+      <c r="I83" s="86" t="n"/>
+      <c r="J83" s="86" t="n"/>
+      <c r="K83" s="86" t="n"/>
+      <c r="L83" s="86" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="86" t="n"/>
+      <c r="B84" s="86" t="n"/>
+      <c r="C84" s="86" t="n"/>
+      <c r="D84" s="86" t="n"/>
+      <c r="E84" s="86" t="n"/>
+      <c r="F84" s="86" t="n"/>
+      <c r="G84" s="86" t="n"/>
+      <c r="H84" s="86" t="n"/>
+      <c r="I84" s="86" t="n"/>
+      <c r="J84" s="86" t="n"/>
+      <c r="K84" s="86" t="n"/>
+      <c r="L84" s="86" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="86" t="n"/>
+      <c r="B85" s="86" t="n"/>
+      <c r="C85" s="86" t="n"/>
+      <c r="D85" s="86" t="n"/>
+      <c r="E85" s="86" t="n"/>
+      <c r="F85" s="86" t="n"/>
+      <c r="G85" s="86" t="n"/>
+      <c r="H85" s="86" t="n"/>
+      <c r="I85" s="86" t="n"/>
+      <c r="J85" s="86" t="n"/>
+      <c r="K85" s="86" t="n"/>
+      <c r="L85" s="86" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="86" t="n"/>
+      <c r="B86" s="86" t="n"/>
+      <c r="C86" s="86" t="n"/>
+      <c r="D86" s="86" t="n"/>
+      <c r="E86" s="86" t="n"/>
+      <c r="F86" s="86" t="n"/>
+      <c r="G86" s="86" t="n"/>
+      <c r="H86" s="86" t="n"/>
+      <c r="I86" s="86" t="n"/>
+      <c r="J86" s="86" t="n"/>
+      <c r="K86" s="86" t="n"/>
+      <c r="L86" s="86" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="86" t="n"/>
+      <c r="B87" s="86" t="n"/>
+      <c r="C87" s="86" t="n"/>
+      <c r="D87" s="86" t="n"/>
+      <c r="E87" s="86" t="n"/>
+      <c r="F87" s="86" t="n"/>
+      <c r="G87" s="86" t="n"/>
+      <c r="H87" s="86" t="n"/>
+      <c r="I87" s="86" t="n"/>
+      <c r="J87" s="86" t="n"/>
+      <c r="K87" s="86" t="n"/>
+      <c r="L87" s="86" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="86" t="n"/>
+      <c r="B88" s="86" t="n"/>
+      <c r="C88" s="86" t="n"/>
+      <c r="D88" s="86" t="n"/>
+      <c r="E88" s="86" t="n"/>
+      <c r="F88" s="86" t="n"/>
+      <c r="G88" s="86" t="n"/>
+      <c r="H88" s="86" t="n"/>
+      <c r="I88" s="86" t="n"/>
+      <c r="J88" s="86" t="n"/>
+      <c r="K88" s="86" t="n"/>
+      <c r="L88" s="86" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="86" t="n"/>
+      <c r="B89" s="86" t="n"/>
+      <c r="C89" s="86" t="n"/>
+      <c r="D89" s="86" t="n"/>
+      <c r="E89" s="86" t="n"/>
+      <c r="F89" s="86" t="n"/>
+      <c r="G89" s="86" t="n"/>
+      <c r="H89" s="86" t="n"/>
+      <c r="I89" s="86" t="n"/>
+      <c r="J89" s="86" t="n"/>
+      <c r="K89" s="86" t="n"/>
+      <c r="L89" s="86" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="86" t="n"/>
+      <c r="B90" s="86" t="n"/>
+      <c r="C90" s="86" t="n"/>
+      <c r="D90" s="86" t="n"/>
+      <c r="E90" s="86" t="n"/>
+      <c r="F90" s="86" t="n"/>
+      <c r="G90" s="86" t="n"/>
+      <c r="H90" s="86" t="n"/>
+      <c r="I90" s="86" t="n"/>
+      <c r="J90" s="86" t="n"/>
+      <c r="K90" s="86" t="n"/>
+      <c r="L90" s="86" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="86" t="n"/>
+      <c r="B91" s="86" t="n"/>
+      <c r="C91" s="86" t="n"/>
+      <c r="D91" s="86" t="n"/>
+      <c r="E91" s="86" t="n"/>
+      <c r="F91" s="86" t="n"/>
+      <c r="G91" s="86" t="n"/>
+      <c r="H91" s="86" t="n"/>
+      <c r="I91" s="86" t="n"/>
+      <c r="J91" s="86" t="n"/>
+      <c r="K91" s="86" t="n"/>
+      <c r="L91" s="86" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="86" t="n"/>
+      <c r="B92" s="86" t="n"/>
+      <c r="C92" s="86" t="n"/>
+      <c r="D92" s="86" t="n"/>
+      <c r="E92" s="86" t="n"/>
+      <c r="F92" s="86" t="n"/>
+      <c r="G92" s="86" t="n"/>
+      <c r="H92" s="86" t="n"/>
+      <c r="I92" s="86" t="n"/>
+      <c r="J92" s="86" t="n"/>
+      <c r="K92" s="86" t="n"/>
+      <c r="L92" s="86" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="86" t="n"/>
+      <c r="B93" s="86" t="n"/>
+      <c r="C93" s="86" t="n"/>
+      <c r="D93" s="86" t="n"/>
+      <c r="E93" s="86" t="n"/>
+      <c r="F93" s="86" t="n"/>
+      <c r="G93" s="86" t="n"/>
+      <c r="H93" s="86" t="n"/>
+      <c r="I93" s="86" t="n"/>
+      <c r="J93" s="86" t="n"/>
+      <c r="K93" s="86" t="n"/>
+      <c r="L93" s="86" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="86" t="n"/>
+      <c r="B94" s="86" t="n"/>
+      <c r="C94" s="86" t="n"/>
+      <c r="D94" s="86" t="n"/>
+      <c r="E94" s="86" t="n"/>
+      <c r="F94" s="86" t="n"/>
+      <c r="G94" s="86" t="n"/>
+      <c r="H94" s="86" t="n"/>
+      <c r="I94" s="86" t="n"/>
+      <c r="J94" s="86" t="n"/>
+      <c r="K94" s="86" t="n"/>
+      <c r="L94" s="86" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="86" t="n"/>
+      <c r="B95" s="86" t="n"/>
+      <c r="C95" s="86" t="n"/>
+      <c r="D95" s="86" t="n"/>
+      <c r="E95" s="86" t="n"/>
+      <c r="F95" s="86" t="n"/>
+      <c r="G95" s="86" t="n"/>
+      <c r="H95" s="86" t="n"/>
+      <c r="I95" s="86" t="n"/>
+      <c r="J95" s="86" t="n"/>
+      <c r="K95" s="86" t="n"/>
+      <c r="L95" s="86" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="86" t="n"/>
+      <c r="B96" s="86" t="n"/>
+      <c r="C96" s="86" t="n"/>
+      <c r="D96" s="86" t="n"/>
+      <c r="E96" s="86" t="n"/>
+      <c r="F96" s="86" t="n"/>
+      <c r="G96" s="86" t="n"/>
+      <c r="H96" s="86" t="n"/>
+      <c r="I96" s="86" t="n"/>
+      <c r="J96" s="86" t="n"/>
+      <c r="K96" s="86" t="n"/>
+      <c r="L96" s="86" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="86" t="n"/>
+      <c r="B97" s="86" t="n"/>
+      <c r="C97" s="86" t="n"/>
+      <c r="D97" s="86" t="n"/>
+      <c r="E97" s="86" t="n"/>
+      <c r="F97" s="86" t="n"/>
+      <c r="G97" s="86" t="n"/>
+      <c r="H97" s="86" t="n"/>
+      <c r="I97" s="86" t="n"/>
+      <c r="J97" s="86" t="n"/>
+      <c r="K97" s="86" t="n"/>
+      <c r="L97" s="86" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="86" t="n"/>
+      <c r="B98" s="86" t="n"/>
+      <c r="C98" s="86" t="n"/>
+      <c r="D98" s="86" t="n"/>
+      <c r="E98" s="86" t="n"/>
+      <c r="F98" s="86" t="n"/>
+      <c r="G98" s="86" t="n"/>
+      <c r="H98" s="86" t="n"/>
+      <c r="I98" s="86" t="n"/>
+      <c r="J98" s="86" t="n"/>
+      <c r="K98" s="86" t="n"/>
+      <c r="L98" s="86" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="86" t="n"/>
+      <c r="B99" s="86" t="n"/>
+      <c r="C99" s="86" t="n"/>
+      <c r="D99" s="86" t="n"/>
+      <c r="E99" s="86" t="n"/>
+      <c r="F99" s="86" t="n"/>
+      <c r="G99" s="86" t="n"/>
+      <c r="H99" s="86" t="n"/>
+      <c r="I99" s="86" t="n"/>
+      <c r="J99" s="86" t="n"/>
+      <c r="K99" s="86" t="n"/>
+      <c r="L99" s="86" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="86" t="n"/>
+      <c r="B100" s="86" t="n"/>
+      <c r="C100" s="86" t="n"/>
+      <c r="D100" s="86" t="n"/>
+      <c r="E100" s="86" t="n"/>
+      <c r="F100" s="86" t="n"/>
+      <c r="G100" s="86" t="n"/>
+      <c r="H100" s="86" t="n"/>
+      <c r="I100" s="86" t="n"/>
+      <c r="J100" s="86" t="n"/>
+      <c r="K100" s="86" t="n"/>
+      <c r="L100" s="86" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="86" t="n"/>
+      <c r="B101" s="86" t="n"/>
+      <c r="C101" s="86" t="n"/>
+      <c r="D101" s="86" t="n"/>
+      <c r="E101" s="86" t="n"/>
+      <c r="F101" s="86" t="n"/>
+      <c r="G101" s="86" t="n"/>
+      <c r="H101" s="86" t="n"/>
+      <c r="I101" s="86" t="n"/>
+      <c r="J101" s="86" t="n"/>
+      <c r="K101" s="86" t="n"/>
+      <c r="L101" s="86" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="86" t="n"/>
+      <c r="B102" s="86" t="n"/>
+      <c r="C102" s="86" t="n"/>
+      <c r="D102" s="86" t="n"/>
+      <c r="E102" s="86" t="n"/>
+      <c r="F102" s="86" t="n"/>
+      <c r="G102" s="86" t="n"/>
+      <c r="H102" s="86" t="n"/>
+      <c r="I102" s="86" t="n"/>
+      <c r="J102" s="86" t="n"/>
+      <c r="K102" s="86" t="n"/>
+      <c r="L102" s="86" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="86" t="n"/>
+      <c r="B103" s="86" t="n"/>
+      <c r="C103" s="86" t="n"/>
+      <c r="D103" s="86" t="n"/>
+      <c r="E103" s="86" t="n"/>
+      <c r="F103" s="86" t="n"/>
+      <c r="G103" s="86" t="n"/>
+      <c r="H103" s="86" t="n"/>
+      <c r="I103" s="86" t="n"/>
+      <c r="J103" s="86" t="n"/>
+      <c r="K103" s="86" t="n"/>
+      <c r="L103" s="86" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="86" t="n"/>
+      <c r="B104" s="86" t="n"/>
+      <c r="C104" s="86" t="n"/>
+      <c r="D104" s="86" t="n"/>
+      <c r="E104" s="86" t="n"/>
+      <c r="F104" s="86" t="n"/>
+      <c r="G104" s="86" t="n"/>
+      <c r="H104" s="86" t="n"/>
+      <c r="I104" s="86" t="n"/>
+      <c r="J104" s="86" t="n"/>
+      <c r="K104" s="86" t="n"/>
+      <c r="L104" s="86" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="86" t="n"/>
+      <c r="B105" s="86" t="n"/>
+      <c r="C105" s="86" t="n"/>
+      <c r="D105" s="86" t="n"/>
+      <c r="E105" s="86" t="n"/>
+      <c r="F105" s="86" t="n"/>
+      <c r="G105" s="86" t="n"/>
+      <c r="H105" s="86" t="n"/>
+      <c r="I105" s="86" t="n"/>
+      <c r="J105" s="86" t="n"/>
+      <c r="K105" s="86" t="n"/>
+      <c r="L105" s="86" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="86" t="n"/>
+      <c r="B106" s="86" t="n"/>
+      <c r="C106" s="86" t="n"/>
+      <c r="D106" s="86" t="n"/>
+      <c r="E106" s="86" t="n"/>
+      <c r="F106" s="86" t="n"/>
+      <c r="G106" s="86" t="n"/>
+      <c r="H106" s="86" t="n"/>
+      <c r="I106" s="86" t="n"/>
+      <c r="J106" s="86" t="n"/>
+      <c r="K106" s="86" t="n"/>
+      <c r="L106" s="86" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="86" t="n"/>
+      <c r="B107" s="86" t="n"/>
+      <c r="C107" s="86" t="n"/>
+      <c r="D107" s="86" t="n"/>
+      <c r="E107" s="86" t="n"/>
+      <c r="F107" s="86" t="n"/>
+      <c r="G107" s="86" t="n"/>
+      <c r="H107" s="86" t="n"/>
+      <c r="I107" s="86" t="n"/>
+      <c r="J107" s="86" t="n"/>
+      <c r="K107" s="86" t="n"/>
+      <c r="L107" s="86" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="86" t="n"/>
+      <c r="B108" s="86" t="n"/>
+      <c r="C108" s="86" t="n"/>
+      <c r="D108" s="86" t="n"/>
+      <c r="E108" s="86" t="n"/>
+      <c r="F108" s="86" t="n"/>
+      <c r="G108" s="86" t="n"/>
+      <c r="H108" s="86" t="n"/>
+      <c r="I108" s="86" t="n"/>
+      <c r="J108" s="86" t="n"/>
+      <c r="K108" s="86" t="n"/>
+      <c r="L108" s="86" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A15:B15"/>
@@ -1844,52 +3077,4 @@
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="72" t="inlineStr">
-        <is>
-          <t>Aselsan A.S.</t>
-        </is>
-      </c>
-      <c r="B1" s="72" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mehmet Akif Ersoy Mahallesi 296. </t>
-        </is>
-      </c>
-      <c r="B2" s="72" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cadde No:16, 06200 Macunköy Yenimahalle / </t>
-        </is>
-      </c>
-      <c r="B3" s="72" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="77" t="inlineStr">
-        <is>
-          <t>Ankara / TÜRKİYE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:B4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>